--- a/back/data/session-planning/session-planning-model.rc1.xlsx
+++ b/back/data/session-planning/session-planning-model.rc1.xlsx
@@ -4767,684 +4767,684 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="10">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>under pressure</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="10">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>defender closing</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="10">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>tight space</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="10">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>pressed</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="10">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>pressure</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="10">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="10">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>passing</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="10">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>keep the ball</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="10">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>keeping the ball</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="10">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>possess</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="10">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>retain</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="10">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>retention</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="10">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>circulate</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="10">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>combine</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="10">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>combination</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>TA02</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="10">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>shot</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="10">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="10">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>shoot</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="10">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>finish</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="10">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>shooting</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+    <row r="40" ht="15.75" customHeight="1" s="10">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="10">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>shoot</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+    <row r="41" ht="15.75" customHeight="1" s="10">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="10">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>finish</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+    <row r="42" ht="15.75" customHeight="1" s="10">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>goal</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="10">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+    <row r="43" ht="15.75" customHeight="1" s="10">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>goal scoring</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="10">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>scoring</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+    <row r="44" ht="15.75" customHeight="1" s="10">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="10">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+    <row r="45" ht="15.75" customHeight="1" s="10">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>chance creation</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="10">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>goal scoring</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="46" ht="15.75" customHeight="1" s="10">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>final third</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="10">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="47" ht="15.75" customHeight="1" s="10">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>attacking third</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="10">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>chance creation</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="48" ht="15.75" customHeight="1" s="10">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>create better shot</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="10">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>final third</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+    <row r="49" ht="15.75" customHeight="1" s="10">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>creating better shot</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="10">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>attacking third</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="50" ht="15.75" customHeight="1" s="10">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>create shot</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="10">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>create better shot</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="51" ht="15.75" customHeight="1" s="10">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>penalty box</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="10">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>creating better shot</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="52" ht="15.75" customHeight="1" s="10">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>in the box</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1" s="10">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>create shot</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="53" ht="15.75" customHeight="1" s="10">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>around the box</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1" s="10">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>penalty box</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+    <row r="54" ht="15.75" customHeight="1" s="10">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>near goal</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1" s="10">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>in the box</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+    <row r="55" ht="15.75" customHeight="1" s="10">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>in front of goal</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="10">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>around the box</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+    <row r="56" ht="15.75" customHeight="1" s="10">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>convert chance</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="10">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>get a shot</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1" s="10">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>near goal</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1" s="10">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>in front of goal</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1" s="10">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>convert chance</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" s="10">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>get a shot</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-    </row>
     <row r="58" ht="15.75" customHeight="1" s="10">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>transition</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>TA01</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="10">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>counter attack</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>TA01</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="10">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>quick break</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>TA01</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="10">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>fast break</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>TA01</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="10">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>break on turnover</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>TA01</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="10">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>restore defensive shape</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>TD01</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="10">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>after being stretched</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>TD01</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="10">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>TD02</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="10">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>prevent counter</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>TD02</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="10">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>press</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="10">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>pressing</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="10">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>counterpress</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="10">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>regain</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="10">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>win it back</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="10">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>turnover</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="10">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>win the ball</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="10">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>winning the ball</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="10">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>isolate attacker</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>D03</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="10">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>stop your player</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>D03</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="10">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>defend the dribbler</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>D03</t>
         </is>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>Primary RPC ID</t>
+          <t>Routed RPC ID</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">

--- a/back/data/session-planning/session-planning-model.rc1.xlsx
+++ b/back/data/session-planning/session-planning-model.rc1.xlsx
@@ -6418,11 +6418,15 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>GP-005</t>
+        </is>
+      </c>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Intentional runtime gap (Cycle 8 §5) — no placeholder mapping. Runtime realization opportunity, not a knowledge deficiency.</t>
+          <t>Approved 2026-10-15 (Christian, A01 decision 1) — Primary Representative Game Problem Translation: Gain Access, based on the approved Goalkeeper Build-Out context (RPC-001) and its scoring condition. No secondary (Cycle 8 §4 deferral retained). Replaces the Cycle 8 §5 intentional runtime gap. Does not by itself authorize candidate constraints derived from vocabulary coverage.</t>
         </is>
       </c>
     </row>
